--- a/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/03_Tasarım Doğrulama, Test ve Onay/EKG-TAS-FRM-03_tasarim_dogrulama_ve_test_sonuc_raporu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/16_Ürün Tasarımı ve Teknik Doğrulama/03_Tasarım Doğrulama, Test ve Onay/EKG-TAS-FRM-03_tasarim_dogrulama_ve_test_sonuc_raporu.xlsx
@@ -852,7 +852,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-FRM-03&amp;C&amp;"Arial,Regular"&amp;11Tasarım Doğrulama ve Test Sonuç Raporu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 28.09.2026
+Revizyon nedeni: Test raporu alanları numune, teknik revizyon, metot, cihaz, ham veri ve karar kaydıyla düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>